--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\IntegrationPSP\Integration\src\test\resources\ExcelResultsFolder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2AE44E-B8FF-4D6C-8761-27E2EF36A966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1B4085-584E-45D7-834D-9E7A605225AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
-    <sheet name="City" sheetId="2" r:id="rId2"/>
-    <sheet name="Country" sheetId="4" r:id="rId3"/>
-    <sheet name="StreetAddress" sheetId="5" r:id="rId4"/>
-    <sheet name="ZipCode" sheetId="6" r:id="rId5"/>
-    <sheet name="Currency" sheetId="7" r:id="rId6"/>
-    <sheet name="ProductName" sheetId="8" r:id="rId7"/>
-    <sheet name="StateCode" sheetId="12" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId2"/>
+    <sheet name="City" sheetId="2" r:id="rId3"/>
+    <sheet name="Country" sheetId="4" r:id="rId4"/>
+    <sheet name="CC1" sheetId="15" r:id="rId5"/>
+    <sheet name="StreetAddress" sheetId="5" r:id="rId6"/>
+    <sheet name="ZipCode" sheetId="6" r:id="rId7"/>
+    <sheet name="Currency" sheetId="7" r:id="rId8"/>
+    <sheet name="ProductName" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId10"/>
+    <sheet name="StateCode" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EmailData!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EmailData!$A$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
   <si>
     <t>US</t>
   </si>
@@ -69,15 +72,6 @@
     <t>TestData</t>
   </si>
   <si>
-    <t>test@example.com</t>
-  </si>
-  <si>
-    <t>user.name@example.com</t>
-  </si>
-  <si>
-    <t>user_name@example.com</t>
-  </si>
-  <si>
     <t>user-name@example.com</t>
   </si>
   <si>
@@ -108,21 +102,9 @@
     <t>user@123.com</t>
   </si>
   <si>
-    <t>user@example.travel</t>
-  </si>
-  <si>
-    <t>testexample.com</t>
-  </si>
-  <si>
-    <t>test@</t>
-  </si>
-  <si>
     <t>@example.com</t>
   </si>
   <si>
-    <t>test@.com</t>
-  </si>
-  <si>
     <t>test@example</t>
   </si>
   <si>
@@ -186,18 +168,6 @@
     <t>New York</t>
   </si>
   <si>
-    <t>Coimbatore-North</t>
-  </si>
-  <si>
-    <t>O'Fallon</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Beijing</t>
-  </si>
-  <si>
     <t>Los Angeles</t>
   </si>
   <si>
@@ -309,39 +279,6 @@
     <t>123 45 678</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>INR</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>GBP</t>
-  </si>
-  <si>
-    <t>JPY</t>
-  </si>
-  <si>
-    <t>AUD</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>CHF</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
-    <t>NZD</t>
-  </si>
-  <si>
     <t>INR1</t>
   </si>
   <si>
@@ -408,16 +345,19 @@
     <t>TN</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>NY1</t>
-  </si>
-  <si>
     <t>@CA</t>
   </si>
   <si>
     <t>#TX</t>
+  </si>
+  <si>
+    <t>123456789012345</t>
+  </si>
+  <si>
+    <t>user_namee@example.com</t>
+  </si>
+  <si>
+    <t>user1234@example.com</t>
   </si>
 </sst>
 </file>
@@ -836,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -855,7 +795,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -872,8 +812,8 @@
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>10</v>
+      <c r="A4" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -882,7 +822,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -890,368 +830,673 @@
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="3:5">
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="3:5">
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
+    <row r="19" spans="3:5">
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="3:5">
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="3:5">
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="3:5">
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="3:5">
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="3:5">
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="3:5">
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="3:5">
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="3:5">
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
+    <row r="28" spans="3:5">
       <c r="C28" s="6"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A25" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6637D890-2080-4B27-954C-BDB942F17670}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C7EBC6-1F7B-4D49-A634-9FC007EF1086}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>123</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
+  <dimension ref="A1:B64"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="13"/>
+      <c r="B61" s="8"/>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
+    <hyperlink ref="A1" r:id="rId2" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A2" r:id="rId3" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2E299D-1153-47D3-ACB1-8EE951B99FA7}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="44.08984375" style="9" customWidth="1"/>
@@ -1270,7 +1515,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>5</v>
@@ -1279,7 +1524,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>5</v>
@@ -1287,7 +1532,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>5</v>
@@ -1297,56 +1542,56 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="B6" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="9" t="s">
-        <v>50</v>
+      <c r="A7" s="9">
+        <v>123</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="9" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="B10" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="9">
-        <v>123</v>
+      <c r="A11" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>6</v>
@@ -1354,41 +1599,9 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="9" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1397,7 +1610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB3DF1E-7FCF-4AC6-A651-95E623130261}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1440,7 +1653,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -1450,7 +1663,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -1460,7 +1673,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -1471,7 +1684,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -1482,7 +1695,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -1493,7 +1706,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -1509,7 +1722,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -1517,7 +1730,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -1533,7 +1746,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -1541,7 +1754,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -1549,7 +1762,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -1557,7 +1770,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -1576,7 +1789,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04D9505-AF88-4263-B8C1-27EB82E956B3}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD81227-AF5E-4F7B-936E-19FF4A5E049F}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1598,7 +1841,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -1607,7 +1850,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -1616,7 +1859,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -1638,7 +1881,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -1649,7 +1892,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -1660,7 +1903,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -1679,7 +1922,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -1690,7 +1933,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -1701,7 +1944,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -1712,7 +1955,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -1720,7 +1963,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -1732,7 +1975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7063156-6C08-4131-917F-AB54D3A5925A}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1794,7 +2037,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>5</v>
@@ -1805,7 +2048,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="12" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>5</v>
@@ -1816,7 +2059,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>5</v>
@@ -1827,7 +2070,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>5</v>
@@ -1847,7 +2090,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>6</v>
@@ -1865,8 +2108,8 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="11">
-        <v>123456789012345</v>
+      <c r="A13" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>6</v>
@@ -1874,7 +2117,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>6</v>
@@ -1882,7 +2125,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>6</v>
@@ -1890,7 +2133,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>6</v>
@@ -1902,9 +2145,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C31D231-2838-4C23-B639-4D266A9B2FCF}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="3"/>
@@ -1923,250 +2166,132 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>5</v>
-      </c>
+      <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="8" t="s">
-        <v>90</v>
+      <c r="A4" s="8">
+        <v>123</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="8" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="8" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="8" t="s">
-        <v>93</v>
+      <c r="A7" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="8" t="s">
-        <v>94</v>
+      <c r="A8" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" s="1"/>
-      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" s="1"/>
-      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" s="1"/>
-      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
-        <v>6</v>
-      </c>
       <c r="C13" s="1"/>
-      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>6</v>
-      </c>
       <c r="C14" s="1"/>
-      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>6</v>
-      </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="8">
-        <v>123</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>6</v>
-      </c>
       <c r="C16" s="1"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="17" spans="3:3">
       <c r="C17" s="1"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="18" spans="3:3">
       <c r="C18" s="1"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="19" spans="3:3">
       <c r="C19" s="1"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="20" spans="3:3">
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="3:3">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="3:3">
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="3:3">
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="3:3">
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="3:3">
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="3:3">
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="3:3">
       <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="3:3">
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="3:3">
-      <c r="C39" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2175,7 +2300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F273D65-64CD-4DA6-A7CB-CBDD420D1D4A}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2204,7 +2329,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>5</v>
@@ -2213,7 +2338,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>5</v>
@@ -2222,7 +2347,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>5</v>
@@ -2231,7 +2356,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>5</v>
@@ -2240,7 +2365,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>5</v>
@@ -2249,7 +2374,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>5</v>
@@ -2257,7 +2382,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>5</v>
@@ -2265,7 +2390,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>5</v>
@@ -2278,7 +2403,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>6</v>
@@ -2286,7 +2411,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>6</v>
@@ -2294,7 +2419,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>6</v>
@@ -2304,158 +2429,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C7EBC6-1F7B-4D49-A634-9FC007EF1086}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="9"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>123</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1B4085-584E-45D7-834D-9E7A605225AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33309943-8C07-4C19-ABB8-0B334A00E8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -803,30 +803,12 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
@@ -946,11 +928,10 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1440,6 +1421,30 @@
         <v>6</v>
       </c>
     </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="54" spans="1:2">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
@@ -1489,6 +1494,7 @@
     <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
     <hyperlink ref="A1" r:id="rId2" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
     <hyperlink ref="A2" r:id="rId3" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+    <hyperlink ref="A46" r:id="rId4" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33309943-8C07-4C19-ABB8-0B334A00E8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7733792E-933E-4E0C-91FF-D2143517D3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -776,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -803,135 +803,230 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
+      <c r="A3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="C6" s="1"/>
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="3:5">
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="3:5">
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="3:5">
+    <row r="19" spans="1:5">
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="3:5">
+    <row r="20" spans="1:5">
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="3:5">
+    <row r="21" spans="1:5">
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="3:5">
+    <row r="22" spans="1:5">
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="3:5">
+    <row r="23" spans="1:5">
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="3:5">
+    <row r="24" spans="1:5">
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="3:5">
+    <row r="25" spans="1:5">
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="3:5">
+    <row r="26" spans="1:5">
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="3:5">
+    <row r="27" spans="1:5">
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="3:5">
-      <c r="C28" s="6"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -1079,140 +1174,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A19:B64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
@@ -1445,17 +1412,69 @@
         <v>5</v>
       </c>
     </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
+      <c r="A54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
+      <c r="A56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="8"/>
@@ -1492,9 +1511,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
-    <hyperlink ref="A1" r:id="rId2" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
-    <hyperlink ref="A2" r:id="rId3" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
-    <hyperlink ref="A46" r:id="rId4" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
+    <hyperlink ref="A46" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1637,86 +1654,38 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1"/>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" s="1"/>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7733792E-933E-4E0C-91FF-D2143517D3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EA1C06-4393-4743-86F4-3442CD48FD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="104">
   <si>
     <t>US</t>
   </si>
@@ -794,8 +794,8 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15" t="s">
-        <v>103</v>
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -803,230 +803,129 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
+    <row r="17" spans="3:5">
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
+    <row r="18" spans="3:5">
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="3:5">
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="3:5">
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="3:5">
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="3:5">
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="3:5">
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="3:5">
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="3:5">
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="3:5">
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="3:5">
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1174,12 +1073,156 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A19:B64"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
@@ -1512,6 +1555,9 @@
   <hyperlinks>
     <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
     <hyperlink ref="A46" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
+    <hyperlink ref="A1" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A2" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A3" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EA1C06-4393-4743-86F4-3442CD48FD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FA574D-6A93-44D1-ABF1-4BE6463DCFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FA574D-6A93-44D1-ABF1-4BE6463DCFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9F5BAE-2419-4945-9A74-BD0118985670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -1681,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB3DF1E-7FCF-4AC6-A651-95E623130261}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="20.453125" customWidth="1"/>
@@ -1691,7 +1691,7 @@
     <col min="6" max="6" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
@@ -1699,109 +1699,72 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="C3" s="1"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="C4" s="1"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="C5" s="1"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5">
+    <row r="2" spans="1:2">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>1234</v>
+      </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>1234</v>
-      </c>
-      <c r="B18" t="s">
         <v>6</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9F5BAE-2419-4945-9A74-BD0118985670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD56FC8F-B0F9-47E2-95DB-6771C9ABE02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -776,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -803,129 +803,462 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
+      <c r="A3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
+      <c r="A5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="3:5">
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="3:5">
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="3:5">
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="3:5">
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="3:5">
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="3:5">
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="3:5">
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="3:5">
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="3:5">
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="3:5">
+    <row r="26" spans="1:5">
+      <c r="A26" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="3:5">
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A26" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
+    <hyperlink ref="A48" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -1073,388 +1406,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A49:B64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" t="s">
-        <v>5</v>
-      </c>
-    </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>3</v>
@@ -1552,13 +1509,6 @@
       <c r="B64" s="8"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
-    <hyperlink ref="A46" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
-    <hyperlink ref="A1" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
-    <hyperlink ref="A2" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
-    <hyperlink ref="A3" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD56FC8F-B0F9-47E2-95DB-6771C9ABE02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B9C542-7024-4060-A03E-91C6EE167E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -776,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -803,462 +803,129 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
+    <row r="17" spans="3:5">
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
+    <row r="18" spans="3:5">
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
+    <row r="19" spans="3:5">
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
+    <row r="20" spans="3:5">
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="3:5">
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="3:5">
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="3:5">
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="3:5">
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="3:5">
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="3:5">
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="3:5">
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
-    <hyperlink ref="A48" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
-  <legacyDrawing r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1406,12 +1073,388 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A49:B64"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>3</v>
@@ -1509,6 +1552,13 @@
       <c r="B64" s="8"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
+    <hyperlink ref="A46" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
+    <hyperlink ref="A1" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A2" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A3" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B9C542-7024-4060-A03E-91C6EE167E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D681FDD-FB2B-4E39-A290-113E24DB82A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="105">
   <si>
     <t>US</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>user1234@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> test123@example.com </t>
   </si>
 </sst>
 </file>
@@ -776,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -795,7 +798,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -803,129 +806,462 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
+      <c r="A3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
+      <c r="A5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="3:5">
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="3:5">
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="3:5">
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="3:5">
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="3:5">
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="3:5">
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="3:5">
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="3:5">
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="3:5">
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="3:5">
+    <row r="26" spans="1:5">
+      <c r="A26" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="3:5">
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A26" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
+    <hyperlink ref="A48" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -1073,385 +1409,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A3:D64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="3" spans="3:4">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1552,13 +1528,6 @@
       <c r="B64" s="8"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
-    <hyperlink ref="A46" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
-    <hyperlink ref="A1" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
-    <hyperlink ref="A2" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
-    <hyperlink ref="A3" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D681FDD-FB2B-4E39-A290-113E24DB82A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221E4040-6536-40DA-ABB1-2FED01B6E9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221E4040-6536-40DA-ABB1-2FED01B6E9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D70DE0-B65E-4590-A30B-26E32278C1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="105">
   <si>
     <t>US</t>
   </si>
@@ -1253,11 +1253,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
-    <hyperlink ref="A48" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+    <hyperlink ref="A26" r:id="rId1" xr:uid="{49ECFA9C-7AE9-4749-BEBC-AC0397F13AB5}"/>
+    <hyperlink ref="A48" r:id="rId2" xr:uid="{F22CC1A1-003A-401C-B979-A531EE70DCFC}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{7A8AB0E2-384D-4019-A412-DB491D13704E}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{F27F000C-E119-40FF-ABF5-E8EE9BA02D4C}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{D09B16E8-84E3-47BF-91C4-2738F49DE2FC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
@@ -1409,13 +1409,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A3:D64"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4">
+    <row r="1" spans="1:4">
+      <c r="A1" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
@@ -1423,11 +1445,361 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:4">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1528,6 +1900,13 @@
       <c r="B64" s="8"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A24" r:id="rId1" xr:uid="{789A740E-171E-4CF3-BE0C-E8575127A181}"/>
+    <hyperlink ref="A46" r:id="rId2" xr:uid="{D538F831-F970-4D28-B2ED-67F6B5B78260}"/>
+    <hyperlink ref="A1" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
+    <hyperlink ref="A2" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
+    <hyperlink ref="A3" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D70DE0-B65E-4590-A30B-26E32278C1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2730F95F-0409-482A-9E22-9C82BE2E7D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.7265625" customWidth="1"/>
@@ -806,462 +806,129 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
+    <row r="17" spans="3:5">
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
+    <row r="18" spans="3:5">
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
+    <row r="19" spans="3:5">
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
+    <row r="20" spans="3:5">
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="3:5">
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="3:5">
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="3:5">
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="3:5">
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="3:5">
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="3:5">
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="3:5">
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" xr:uid="{49ECFA9C-7AE9-4749-BEBC-AC0397F13AB5}"/>
-    <hyperlink ref="A48" r:id="rId2" xr:uid="{F22CC1A1-003A-401C-B979-A531EE70DCFC}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{7A8AB0E2-384D-4019-A412-DB491D13704E}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{F27F000C-E119-40FF-ABF5-E8EE9BA02D4C}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{D09B16E8-84E3-47BF-91C4-2738F49DE2FC}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
-  <legacyDrawing r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1409,13 +1076,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B504D2B0-7F8F-4D5C-968B-FD65C5552841}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="15" t="s">
         <v>103</v>
       </c>
@@ -1423,7 +1090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" s="15" t="s">
         <v>102</v>
       </c>
@@ -1431,7 +1098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3" s="15" t="s">
         <v>102</v>
       </c>
@@ -1444,8 +1111,14 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="F3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1458,360 +1131,638 @@
       <c r="D4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="F4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="F5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="F26" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="F29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="F30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="F31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="F32" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="F37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
+      <c r="F38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>27</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:2">
+      <c r="F39" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>28</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
+      <c r="F40" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>29</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
+      <c r="F41" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="F42" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>31</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
+      <c r="F44" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>9</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="15" t="s">
         <v>102</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>8</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="F48" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="G48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>3</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -1819,7 +1770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>47</v>
       </c>
@@ -1827,7 +1778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>48</v>
       </c>
@@ -1835,7 +1786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -1843,7 +1794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -1851,7 +1802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -1859,7 +1810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>52</v>
       </c>
@@ -1867,35 +1818,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:7">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:7">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:7">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:7">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:7">
       <c r="A61" s="13"/>
       <c r="B61" s="8"/>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:7">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:7">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:7">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
     </row>
@@ -1906,6 +1857,11 @@
     <hyperlink ref="A1" r:id="rId3" xr:uid="{AC1FEB32-C77C-4A05-881A-951B5085049D}"/>
     <hyperlink ref="A2" r:id="rId4" xr:uid="{B4063AA3-3091-48C5-8A69-3CE41471BCF0}"/>
     <hyperlink ref="A3" r:id="rId5" xr:uid="{CA38208A-ED34-42D1-B3BD-5752BE432ABD}"/>
+    <hyperlink ref="F26" r:id="rId6" xr:uid="{49ECFA9C-7AE9-4749-BEBC-AC0397F13AB5}"/>
+    <hyperlink ref="F48" r:id="rId7" xr:uid="{F22CC1A1-003A-401C-B979-A531EE70DCFC}"/>
+    <hyperlink ref="F3" r:id="rId8" xr:uid="{7A8AB0E2-384D-4019-A412-DB491D13704E}"/>
+    <hyperlink ref="F4" r:id="rId9" xr:uid="{F27F000C-E119-40FF-ABF5-E8EE9BA02D4C}"/>
+    <hyperlink ref="F5" r:id="rId10" xr:uid="{D09B16E8-84E3-47BF-91C4-2738F49DE2FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2730F95F-0409-482A-9E22-9C82BE2E7D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E34B74E-474E-4565-8854-9B37F2F6E408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="105">
   <si>
     <t>US</t>
   </si>
@@ -806,20 +806,50 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E34B74E-474E-4565-8854-9B37F2F6E408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7BDAE2-6BF5-48EC-BEA8-6D50CAB62093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="105">
   <si>
     <t>US</t>
   </si>
@@ -2295,7 +2295,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7063156-6C08-4131-917F-AB54D3A5925A}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="11" customWidth="1"/>
@@ -2322,18 +2322,19 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11">
-        <v>560001</v>
+      <c r="A3" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12">
-        <v>10001</v>
+      <c r="A4" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>5</v>
@@ -2343,8 +2344,8 @@
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12">
-        <v>90210</v>
+      <c r="A5" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>5</v>
@@ -2355,7 +2356,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>5</v>
@@ -2365,95 +2366,62 @@
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12" t="s">
-        <v>70</v>
-      </c>
+      <c r="A7" s="12"/>
       <c r="B7" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12" t="s">
-        <v>71</v>
+      <c r="A8" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12" t="s">
-        <v>72</v>
+      <c r="A9" s="11">
+        <v>1234</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="12"/>
+      <c r="A10" s="12" t="s">
+        <v>101</v>
+      </c>
       <c r="B10" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="11">
-        <v>1234</v>
+      <c r="A12" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12" t="s">
-        <v>101</v>
+      <c r="A13" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="12" t="s">
         <v>6</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7BDAE2-6BF5-48EC-BEA8-6D50CAB62093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F274298-F2C5-4132-883C-C2C1CC22AF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -806,50 +806,20 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1799,6 +1769,12 @@
       <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
@@ -1807,6 +1783,12 @@
       <c r="B51" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
@@ -1815,6 +1797,12 @@
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
@@ -1823,12 +1811,24 @@
       <c r="B53" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s">
         <v>5</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F274298-F2C5-4132-883C-C2C1CC22AF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE23C0DC-CC3B-4B30-AE2E-C4F8535B8099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EmailData" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="105">
   <si>
     <t>US</t>
   </si>
@@ -806,9 +806,21 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">

--- a/src/test/resources/ExcelResultsFolder/TestData.xlsx
+++ b/src/test/resources/ExcelResultsFolder/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE23C0DC-CC3B-4B30-AE2E-C4F8535B8099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08887617-3032-45DE-8AB5-A20747E56B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="105">
   <si>
     <t>US</t>
   </si>
@@ -807,140 +807,275 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5">
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="3:5">
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="3:5">
+    <row r="18" spans="1:5">
+      <c r="A18" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="3:5">
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="3:5">
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="3:5">
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="3:5">
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="3:5">
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="3:5">
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="3:5">
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="3:5">
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="3:5">
+    <row r="27" spans="1:5">
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A18" r:id="rId1" xr:uid="{D44C2EF8-E7EA-402E-9187-B5F88FA1D86D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1092,6 +1227,7 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="6" max="6" width="40.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1851,12 +1987,24 @@
       <c r="B55" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s">
         <v>5</v>
       </c>
     </row>
